--- a/bom.xlsx
+++ b/bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0E8AEF-2BFA-4F09-A919-A410DC804F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F87104-C344-429A-A508-46544CFF058A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFCCF245-3A95-42B6-B6AF-3F5B4AE0B2A2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
   <si>
     <t>name</t>
   </si>
@@ -117,9 +117,6 @@
   </si>
   <si>
     <t>rotary encoder</t>
-  </si>
-  <si>
-    <t>reichelt.at</t>
   </si>
   <si>
     <t>printing legion*</t>
@@ -183,6 +180,9 @@
   </si>
   <si>
     <t>dollars</t>
+  </si>
+  <si>
+    <t>note: I am buying them 2 times</t>
   </si>
 </sst>
 </file>
@@ -227,7 +227,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,12 +270,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -432,7 +426,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -447,7 +441,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -494,9 +487,8 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -833,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E64C7CD-047A-4149-A2FB-275886201874}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -841,20 +833,20 @@
     <col min="8" max="8" width="18.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-    </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -883,7 +875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -912,45 +904,45 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="14"/>
+      <c r="C4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="14"/>
+      <c r="C5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="13"/>
       <c r="I5" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>4</v>
       </c>
@@ -979,7 +971,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1001,97 +993,99 @@
       <c r="G7" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="24" t="s">
         <v>3</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3">
-        <v>48.89</v>
-      </c>
-      <c r="D8" s="3">
-        <v>8.01</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="3">
-        <v>56.9</v>
+      <c r="C8" s="27">
+        <v>9.77</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="26">
+        <f>C8*2</f>
+        <v>19.54</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <v>6.04</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="26">
+      <c r="D9" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="25">
         <v>6.04</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="24" t="s">
         <v>3</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="26">
+        <v>33</v>
+      </c>
+      <c r="C10" s="25">
         <v>5.0199999999999996</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="26">
+      <c r="D10" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="25">
         <v>5.0199999999999996</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="24" t="s">
         <v>3</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1113,14 +1107,14 @@
       <c r="G11" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="24" t="s">
         <v>3</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1142,131 +1136,131 @@
       <c r="G12" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="24" t="s">
         <v>3</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="27">
+        <v>32</v>
+      </c>
+      <c r="C13" s="26">
         <v>34.99</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="27">
         <v>4.99</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="27">
         <f>+D13+C13</f>
         <v>39.980000000000004</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="24" t="s">
         <v>3</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="26">
+        <v>34</v>
+      </c>
+      <c r="C14" s="25">
         <v>6.74</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="26">
+      <c r="D14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="25">
         <v>6.74</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="24" t="s">
         <v>3</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="28">
+        <f>F14+F10+F9+F8</f>
+        <v>37.340000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="E17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="30">
-        <f>F14+F10+F9</f>
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E17" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="31">
+      <c r="F17" s="5">
         <f>F12+F11+F7+F3</f>
         <v>89.35</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="17"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="19" t="s">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="21"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="19" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="21"/>
-    </row>
-    <row r="24" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="24"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="D9:E9"/>
@@ -1277,16 +1271,17 @@
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
+    <mergeCell ref="D8:E8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="H8" r:id="rId1" xr:uid="{237C3B41-25EE-4885-838A-18647F8863FB}"/>
-    <hyperlink ref="H7" r:id="rId2" xr:uid="{4FB13AFD-827D-46AC-859D-4BF6EEDE45AC}"/>
-    <hyperlink ref="H9" r:id="rId3" xr:uid="{4C4E8E23-ABEE-4ACB-B8B4-5573DE6B7A1A}"/>
-    <hyperlink ref="H10" r:id="rId4" xr:uid="{67AF882D-6007-42CA-A0F2-994960EF2A36}"/>
-    <hyperlink ref="H14" r:id="rId5" xr:uid="{6AB4648A-FCAC-4DB4-B3DA-9C9BB7B982AA}"/>
-    <hyperlink ref="H13" r:id="rId6" xr:uid="{6AF62CB0-E0A4-4318-991B-3C0E5F25CA0D}"/>
-    <hyperlink ref="H11" r:id="rId7" xr:uid="{9662131F-50DC-45DC-B044-76403E3E1ECB}"/>
-    <hyperlink ref="H12" r:id="rId8" xr:uid="{9A785BE8-423E-4D7F-8EB2-CA7C8AB0A98C}"/>
+    <hyperlink ref="H7" r:id="rId1" xr:uid="{4FB13AFD-827D-46AC-859D-4BF6EEDE45AC}"/>
+    <hyperlink ref="H9" r:id="rId2" xr:uid="{4C4E8E23-ABEE-4ACB-B8B4-5573DE6B7A1A}"/>
+    <hyperlink ref="H10" r:id="rId3" xr:uid="{67AF882D-6007-42CA-A0F2-994960EF2A36}"/>
+    <hyperlink ref="H14" r:id="rId4" xr:uid="{6AB4648A-FCAC-4DB4-B3DA-9C9BB7B982AA}"/>
+    <hyperlink ref="H13" r:id="rId5" xr:uid="{6AF62CB0-E0A4-4318-991B-3C0E5F25CA0D}"/>
+    <hyperlink ref="H11" r:id="rId6" xr:uid="{9662131F-50DC-45DC-B044-76403E3E1ECB}"/>
+    <hyperlink ref="H12" r:id="rId7" xr:uid="{9A785BE8-423E-4D7F-8EB2-CA7C8AB0A98C}"/>
+    <hyperlink ref="H8" r:id="rId8" xr:uid="{8745AF16-B382-486E-AA37-684560A37C0A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
